--- a/fixtures/seed_data.xlsx
+++ b/fixtures/seed_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\feevert-pro\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06E1B94-FD12-4679-80C8-6F7F91CC82F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8C01A8-F871-4755-8A67-DFA6770D02E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="16656" windowHeight="10680" firstSheet="14" activeTab="18" xr2:uid="{D15F9AC0-767E-4280-9552-DDD9367DD8A3}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="12684" windowHeight="10680" activeTab="2" xr2:uid="{D15F9AC0-767E-4280-9552-DDD9367DD8A3}"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" r:id="rId1"/>
@@ -4458,7 +4458,16 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="18.44140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="11.77734375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -5941,7 +5950,13 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="26.5546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -5970,7 +5985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="216" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
@@ -5996,7 +6011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>25</v>
       </c>
@@ -6022,7 +6037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
@@ -6048,7 +6063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
@@ -6074,7 +6089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="126.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>37</v>
       </c>
@@ -6100,7 +6115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
@@ -6126,7 +6141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>45</v>
       </c>
@@ -6152,7 +6167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="216" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>49</v>
       </c>
@@ -6178,7 +6193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="121.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>52</v>
       </c>
@@ -6204,7 +6219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>56</v>
       </c>
@@ -6215,7 +6230,7 @@
         <v>58</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
@@ -6256,7 +6271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="216" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>64</v>
       </c>
@@ -6282,7 +6297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>68</v>
       </c>
@@ -6308,7 +6323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>72</v>
       </c>
@@ -6334,7 +6349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>76</v>
       </c>
@@ -6360,7 +6375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="95.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>80</v>
       </c>
@@ -6386,7 +6401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="103.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>84</v>
       </c>
@@ -6412,7 +6427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="216" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="128.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>88</v>
       </c>
@@ -6438,7 +6453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>91</v>
       </c>
@@ -6490,7 +6505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>99</v>
       </c>

--- a/fixtures/seed_data.xlsx
+++ b/fixtures/seed_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\projects\feevert-pro\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A767EF2A-2957-4CFE-9DF4-56901EC868BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE4B67D-D2B3-4FBA-A65C-F816E6DBFCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1620" windowWidth="27465" windowHeight="13815" firstSheet="1" activeTab="6" xr2:uid="{D15F9AC0-767E-4280-9552-DDD9367DD8A3}"/>
+    <workbookView xWindow="345" yWindow="1965" windowWidth="27465" windowHeight="13815" firstSheet="1" activeTab="9" xr2:uid="{D15F9AC0-767E-4280-9552-DDD9367DD8A3}"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" r:id="rId1"/>
@@ -22,24 +22,25 @@
     <sheet name="team" sheetId="7" r:id="rId7"/>
     <sheet name="site_settings" sheetId="8" r:id="rId8"/>
     <sheet name="hero_slides" sheetId="9" r:id="rId9"/>
-    <sheet name="about" sheetId="10" r:id="rId10"/>
-    <sheet name="testimonials" sheetId="11" r:id="rId11"/>
-    <sheet name="partners" sheetId="12" r:id="rId12"/>
-    <sheet name="faqs" sheetId="13" r:id="rId13"/>
-    <sheet name="news_categories" sheetId="14" r:id="rId14"/>
-    <sheet name="news" sheetId="15" r:id="rId15"/>
-    <sheet name="job_categories" sheetId="16" r:id="rId16"/>
-    <sheet name="jobs" sheetId="17" r:id="rId17"/>
-    <sheet name="time_slots" sheetId="18" r:id="rId18"/>
-    <sheet name="product_categories" sheetId="20" r:id="rId19"/>
-    <sheet name="products" sheetId="19" r:id="rId20"/>
+    <sheet name="what_we_do" sheetId="21" r:id="rId10"/>
+    <sheet name="about" sheetId="10" r:id="rId11"/>
+    <sheet name="testimonials" sheetId="11" r:id="rId12"/>
+    <sheet name="partners" sheetId="12" r:id="rId13"/>
+    <sheet name="faqs" sheetId="13" r:id="rId14"/>
+    <sheet name="news_categories" sheetId="14" r:id="rId15"/>
+    <sheet name="news" sheetId="15" r:id="rId16"/>
+    <sheet name="job_categories" sheetId="16" r:id="rId17"/>
+    <sheet name="jobs" sheetId="17" r:id="rId18"/>
+    <sheet name="time_slots" sheetId="18" r:id="rId19"/>
+    <sheet name="product_categories" sheetId="20" r:id="rId20"/>
+    <sheet name="products" sheetId="19" r:id="rId21"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1152">
   <si>
     <t>name</t>
   </si>
@@ -3447,6 +3448,54 @@
   </si>
   <si>
     <t>estimated_delivery_days</t>
+  </si>
+  <si>
+    <t>slider_images</t>
+  </si>
+  <si>
+    <t>Agriculture &amp; Agribusiness</t>
+  </si>
+  <si>
+    <t>Sustainable farming for a food-secure future</t>
+  </si>
+  <si>
+    <t>We provide expert agricultural consultancy including sustainable farming practices, crop management, livestock production, agribusiness development, and market linkage services to empower farmers and agribusinesses across Tanzania.</t>
+  </si>
+  <si>
+    <t>Learn More</t>
+  </si>
+  <si>
+    <t>Environment &amp; Sustainability</t>
+  </si>
+  <si>
+    <t>Protecting our planet for future generations</t>
+  </si>
+  <si>
+    <t>We offer comprehensive environmental solutions including Environmental Impact Assessments (EIA), natural resource management, climate change adaptation, waste management, and sustainability consulting for businesses and communities.</t>
+  </si>
+  <si>
+    <t>Creating safer workplaces for all</t>
+  </si>
+  <si>
+    <t>We deliver professional Occupational Health &amp; Safety (OHS) services including workplace safety audits, risk assessments, safety training, compliance certification, and development of comprehensive safety management systems.</t>
+  </si>
+  <si>
+    <t>[{"icon": "ðŸŒ¾", "title": "Sustainable Farming", "description": "Climate-smart and regenerative agricultural practices"}, {"icon": "ðŸŒ¿", "title": "Crop Management", "description": "Optimized crop production and pest management"}, {"icon": "ðŸ„", "title": "Livestock Production", "description": "Modern livestock farming and animal health"}, {"icon": "ðŸ“ˆ", "title": "Agribusiness Development", "description": "Value addition and market access strategies"}]</t>
+  </si>
+  <si>
+    <t>["/media/whatwedo/agriculture1.jpg", "/media/whatwedo/agriculture2.jpg", "/media/whatwedo/agriculture3.jpg"]</t>
+  </si>
+  <si>
+    <t>[{"icon": "ðŸŒ", "title": "Environmental Impact Assessment", "description": "Comprehensive EIA and environmental auditing"}, {"icon": "ðŸŒ³", "title": "Natural Resource Management", "description": "Sustainable use of forests, water, and land resources"}, {"icon": "â˜€ï¸", "title": "Climate Change Adaptation", "description": "Building resilience to climate impacts"}, {"icon": "â™»ï¸", "title": "Waste Management", "description": "Sustainable waste reduction and recycling solutions"}]</t>
+  </si>
+  <si>
+    <t>["/media/whatwedo/environment1.jpg", "/media/whatwedo/environment2.jpg", "/media/whatwedo/environment3.jpg"]</t>
+  </si>
+  <si>
+    <t>[{"icon": "ðŸ›¡ï¸", "title": "Workplace Safety Audits", "description": "Comprehensive safety inspections and audits"}, {"icon": "ðŸ“‹", "title": "Risk Assessment", "description": "Identifying and mitigating workplace hazards"}, {"icon": "ðŸŽ“", "title": "Safety Training", "description": "OSHA-compliant safety training programs"}, {"icon": "ðŸ“œ", "title": "Compliance Certification", "description": "ISO and OHSAS certification support"}]</t>
+  </si>
+  <si>
+    <t>["/media/whatwedo/ohs1.jpg", "/media/whatwedo/ohs2.jpg", "/media/whatwedo/ohs3.jpg"]</t>
   </si>
 </sst>
 </file>
@@ -4454,6 +4503,132 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD852C7-8354-49FC-8553-95BE838DEE92}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>670</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F1" t="s">
+        <v>608</v>
+      </c>
+      <c r="G1" t="s">
+        <v>609</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G2" t="s">
+        <v>620</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G3" t="s">
+        <v>620</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G4" t="s">
+        <v>620</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F3F04D5-61C4-4B30-8A06-C045F2141E9E}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4538,7 +4713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C50662-CF91-41AE-B52B-AFA2B5D82480}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4735,7 +4910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8CD491-F076-4556-A605-9CFE286E126D}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4857,7 +5032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09238CB1-91DE-4436-B5B6-E52B3F2CF5B5}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5040,7 +5215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6A0E93-D86B-4E92-AB02-5CBD55D8375A}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5151,7 +5326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D343E306-3BC7-47D2-A729-9EEBD18F5956}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5283,7 +5458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BBBD1D-D7BF-4134-8DE5-5DDB27B17536}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5376,7 +5551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81FD2C6-F68E-439D-957F-F3221C8CB20C}">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5629,7 +5804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C0D8A8-EE37-4C71-8C45-F7CC1012C0DE}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5774,260 +5949,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385515EA-DA7E-4346-B807-50FE28B7CF71}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="8.85546875" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>967</v>
-      </c>
-      <c r="B2" t="s">
-        <v>776</v>
-      </c>
-      <c r="C2" t="s">
-        <v>968</v>
-      </c>
-      <c r="D2" t="s">
-        <v>990</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>969</v>
-      </c>
-      <c r="B3" t="s">
-        <v>810</v>
-      </c>
-      <c r="C3" t="s">
-        <v>970</v>
-      </c>
-      <c r="D3" t="s">
-        <v>991</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>971</v>
-      </c>
-      <c r="B4" t="s">
-        <v>950</v>
-      </c>
-      <c r="C4" t="s">
-        <v>972</v>
-      </c>
-      <c r="D4" t="s">
-        <v>992</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>973</v>
-      </c>
-      <c r="B5" t="s">
-        <v>960</v>
-      </c>
-      <c r="C5" t="s">
-        <v>974</v>
-      </c>
-      <c r="D5" t="s">
-        <v>993</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>975</v>
-      </c>
-      <c r="B6" t="s">
-        <v>976</v>
-      </c>
-      <c r="C6" t="s">
-        <v>977</v>
-      </c>
-      <c r="D6" t="s">
-        <v>994</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>978</v>
-      </c>
-      <c r="B7" t="s">
-        <v>865</v>
-      </c>
-      <c r="C7" t="s">
-        <v>979</v>
-      </c>
-      <c r="D7" t="s">
-        <v>995</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>980</v>
-      </c>
-      <c r="B8" t="s">
-        <v>837</v>
-      </c>
-      <c r="C8" t="s">
-        <v>981</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8">
-        <v>7</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>982</v>
-      </c>
-      <c r="B9" t="s">
-        <v>886</v>
-      </c>
-      <c r="C9" t="s">
-        <v>983</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9">
-        <v>8</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>984</v>
-      </c>
-      <c r="B10" t="s">
-        <v>903</v>
-      </c>
-      <c r="C10" t="s">
-        <v>985</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>986</v>
-      </c>
-      <c r="B11" t="s">
-        <v>940</v>
-      </c>
-      <c r="C11" t="s">
-        <v>987</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6707,6 +6628,260 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385515EA-DA7E-4346-B807-50FE28B7CF71}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="8.85546875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C2" t="s">
+        <v>968</v>
+      </c>
+      <c r="D2" t="s">
+        <v>990</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>969</v>
+      </c>
+      <c r="B3" t="s">
+        <v>810</v>
+      </c>
+      <c r="C3" t="s">
+        <v>970</v>
+      </c>
+      <c r="D3" t="s">
+        <v>991</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>971</v>
+      </c>
+      <c r="B4" t="s">
+        <v>950</v>
+      </c>
+      <c r="C4" t="s">
+        <v>972</v>
+      </c>
+      <c r="D4" t="s">
+        <v>992</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>973</v>
+      </c>
+      <c r="B5" t="s">
+        <v>960</v>
+      </c>
+      <c r="C5" t="s">
+        <v>974</v>
+      </c>
+      <c r="D5" t="s">
+        <v>993</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>975</v>
+      </c>
+      <c r="B6" t="s">
+        <v>976</v>
+      </c>
+      <c r="C6" t="s">
+        <v>977</v>
+      </c>
+      <c r="D6" t="s">
+        <v>994</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>978</v>
+      </c>
+      <c r="B7" t="s">
+        <v>865</v>
+      </c>
+      <c r="C7" t="s">
+        <v>979</v>
+      </c>
+      <c r="D7" t="s">
+        <v>995</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>980</v>
+      </c>
+      <c r="B8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C8" t="s">
+        <v>981</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>982</v>
+      </c>
+      <c r="B9" t="s">
+        <v>886</v>
+      </c>
+      <c r="C9" t="s">
+        <v>983</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>984</v>
+      </c>
+      <c r="B10" t="s">
+        <v>903</v>
+      </c>
+      <c r="C10" t="s">
+        <v>985</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>986</v>
+      </c>
+      <c r="B11" t="s">
+        <v>940</v>
+      </c>
+      <c r="C11" t="s">
+        <v>987</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C092ADA5-B033-4E13-9F27-5EC471B6C38B}">
   <dimension ref="A1:AR24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
